--- a/数据对比/cn队数据整理/year6-s1-R1.xlsx
+++ b/数据对比/cn队数据整理/year6-s1-R1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\best igl wiki\数据对比\cn指挥数据对比\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\best igl wiki\数据对比\cn队数据整理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F9819F-6002-4431-8EF5-D1DDFB4F43DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5243BC30-4F0B-4AD4-B869-CC00C3A40DFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-31087" yWindow="-109" windowWidth="31196" windowHeight="18974" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -246,10 +246,10 @@
     <numFmt numFmtId="191" formatCode="[Color13][&gt;0.06]0.0%;[Color3][&lt;0.04]0.0%;[Color10]0.0%"/>
     <numFmt numFmtId="192" formatCode="[Color13][&gt;0.3]0.0%;[Color3][&lt;0.2]0.0%;[Color10]0.0%"/>
     <numFmt numFmtId="193" formatCode="[Color13][&gt;1000]0.00;[Color3][&lt;600]0.00;[Color10]0.00"/>
-    <numFmt numFmtId="195" formatCode="[Color13][&gt;2300]0.00;[Color3][&lt;1900]0.00;[Color10]0.00"/>
-    <numFmt numFmtId="196" formatCode="[Color13][&gt;5.8]0.00;[Color3][&lt;4.7]0.00;[Color10]0.00"/>
-    <numFmt numFmtId="197" formatCode="[Color13][&gt;3.1]0.00;[Color3][&lt;2]0.00;[Color10]0.00"/>
-    <numFmt numFmtId="198" formatCode="[Color13][&gt;3.2]0.00;[Color3][&lt;2.1]0.00;[Color10]0.00"/>
+    <numFmt numFmtId="194" formatCode="[Color13][&gt;2300]0.00;[Color3][&lt;1900]0.00;[Color10]0.00"/>
+    <numFmt numFmtId="195" formatCode="[Color13][&gt;5.8]0.00;[Color3][&lt;4.7]0.00;[Color10]0.00"/>
+    <numFmt numFmtId="196" formatCode="[Color13][&gt;3.1]0.00;[Color3][&lt;2]0.00;[Color10]0.00"/>
+    <numFmt numFmtId="197" formatCode="[Color13][&gt;3.2]0.00;[Color3][&lt;2.1]0.00;[Color10]0.00"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -343,17 +343,11 @@
     <xf numFmtId="188" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="189" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="190" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="191" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -362,6 +356,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="193" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="194" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="195" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -373,8 +370,11 @@
     <xf numFmtId="197" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="198" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -666,11 +666,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
       <c r="D1" s="9" t="s">
         <v>0</v>
       </c>
@@ -726,15 +726,15 @@
       <c r="AB1" s="1"/>
     </row>
     <row r="2" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
       <c r="D2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="20">
+      <c r="E2" s="19">
         <v>1</v>
       </c>
       <c r="F2" s="10">
@@ -773,7 +773,7 @@
       <c r="P2" s="15">
         <v>0.88900000000000001</v>
       </c>
-      <c r="Q2" s="21">
+      <c r="Q2" s="20">
         <v>0.25</v>
       </c>
       <c r="R2" s="1"/>
@@ -789,14 +789,14 @@
       <c r="AB2" s="1"/>
     </row>
     <row r="3" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="19"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
+      <c r="A3" s="28"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
       <c r="D3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="20">
-        <v>3</v>
+      <c r="E3" s="19">
+        <v>2</v>
       </c>
       <c r="F3" s="12">
         <v>12</v>
@@ -834,7 +834,7 @@
       <c r="P3" s="15">
         <v>0.66700000000000004</v>
       </c>
-      <c r="Q3" s="21">
+      <c r="Q3" s="20">
         <v>0.16700000000000001</v>
       </c>
       <c r="R3" s="1"/>
@@ -850,14 +850,14 @@
       <c r="AB3" s="1"/>
     </row>
     <row r="4" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="19"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
       <c r="D4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="20">
-        <v>20</v>
+      <c r="E4" s="19">
+        <v>19</v>
       </c>
       <c r="F4" s="12">
         <v>12</v>
@@ -895,7 +895,7 @@
       <c r="P4" s="15">
         <v>0.25</v>
       </c>
-      <c r="Q4" s="21">
+      <c r="Q4" s="20">
         <v>0</v>
       </c>
       <c r="R4" s="1"/>
@@ -911,14 +911,14 @@
       <c r="AB4" s="1"/>
     </row>
     <row r="5" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
+      <c r="A5" s="28"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
       <c r="D5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="20">
-        <v>5</v>
+      <c r="E5" s="19">
+        <v>4</v>
       </c>
       <c r="F5" s="12">
         <v>12</v>
@@ -956,7 +956,7 @@
       <c r="P5" s="15">
         <v>0.625</v>
       </c>
-      <c r="Q5" s="21">
+      <c r="Q5" s="20">
         <v>0.4</v>
       </c>
       <c r="R5" s="11"/>
@@ -972,13 +972,13 @@
       <c r="AB5" s="11"/>
     </row>
     <row r="6" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="19"/>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
+      <c r="A6" s="28"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="28"/>
       <c r="D6" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="19">
         <v>22</v>
       </c>
       <c r="F6" s="12">
@@ -1017,7 +1017,7 @@
       <c r="P6" s="15">
         <v>0.375</v>
       </c>
-      <c r="Q6" s="21">
+      <c r="Q6" s="20">
         <v>0</v>
       </c>
       <c r="R6" s="11"/>
@@ -1033,11 +1033,11 @@
       <c r="AB6" s="11"/>
     </row>
     <row r="7" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
       <c r="D7" s="12" t="s">
         <v>0</v>
       </c>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="O7" s="12"/>
       <c r="P7" s="12"/>
-      <c r="Q7" s="21"/>
+      <c r="Q7" s="20"/>
       <c r="R7" s="12"/>
       <c r="S7" s="12"/>
       <c r="T7" s="12"/>
@@ -1087,15 +1087,15 @@
       <c r="AB7" s="12"/>
     </row>
     <row r="8" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
       <c r="D8" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="19">
         <v>1</v>
       </c>
       <c r="F8" s="12">
@@ -1124,13 +1124,13 @@
         <f t="shared" ref="M8:M17" si="4">K8-L8</f>
         <v>2652</v>
       </c>
-      <c r="N8" s="25">
+      <c r="N8" s="23">
         <f t="shared" ref="N8:N17" si="5">K8/F8</f>
         <v>1194.5</v>
       </c>
       <c r="O8" s="15"/>
       <c r="P8" s="15"/>
-      <c r="Q8" s="21"/>
+      <c r="Q8" s="20"/>
       <c r="R8" s="12"/>
       <c r="S8" s="12"/>
       <c r="T8" s="12"/>
@@ -1144,14 +1144,14 @@
       <c r="AB8" s="12"/>
     </row>
     <row r="9" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="19"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
+      <c r="A9" s="28"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="28"/>
       <c r="D9" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="20">
-        <v>3</v>
+      <c r="E9" s="19">
+        <v>2</v>
       </c>
       <c r="F9" s="12">
         <v>12</v>
@@ -1179,13 +1179,13 @@
         <f t="shared" si="4"/>
         <v>8738</v>
       </c>
-      <c r="N9" s="25">
+      <c r="N9" s="23">
         <f t="shared" si="5"/>
         <v>1675.9166666666667</v>
       </c>
       <c r="O9" s="15"/>
       <c r="P9" s="15"/>
-      <c r="Q9" s="21"/>
+      <c r="Q9" s="20"/>
       <c r="R9" s="12"/>
       <c r="S9" s="12"/>
       <c r="T9" s="12"/>
@@ -1199,14 +1199,14 @@
       <c r="AB9" s="12"/>
     </row>
     <row r="10" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="19"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="28"/>
       <c r="D10" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="20">
-        <v>20</v>
+      <c r="E10" s="19">
+        <v>19</v>
       </c>
       <c r="F10" s="12">
         <v>12</v>
@@ -1234,13 +1234,13 @@
         <f t="shared" si="4"/>
         <v>-702</v>
       </c>
-      <c r="N10" s="25">
+      <c r="N10" s="23">
         <f t="shared" si="5"/>
         <v>775.41666666666663</v>
       </c>
       <c r="O10" s="15"/>
       <c r="P10" s="15"/>
-      <c r="Q10" s="21"/>
+      <c r="Q10" s="20"/>
       <c r="R10" s="12"/>
       <c r="S10" s="12"/>
       <c r="T10" s="12"/>
@@ -1254,14 +1254,14 @@
       <c r="AB10" s="12"/>
     </row>
     <row r="11" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="19"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
+      <c r="A11" s="28"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="28"/>
       <c r="D11" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="20">
-        <v>5</v>
+      <c r="E11" s="19">
+        <v>4</v>
       </c>
       <c r="F11" s="12">
         <v>12</v>
@@ -1289,13 +1289,13 @@
         <f t="shared" si="4"/>
         <v>4019</v>
       </c>
-      <c r="N11" s="25">
+      <c r="N11" s="23">
         <f t="shared" si="5"/>
         <v>1144.0833333333333</v>
       </c>
       <c r="O11" s="15"/>
       <c r="P11" s="15"/>
-      <c r="Q11" s="21"/>
+      <c r="Q11" s="20"/>
       <c r="R11" s="12"/>
       <c r="S11" s="12"/>
       <c r="T11" s="12"/>
@@ -1309,13 +1309,13 @@
       <c r="AB11" s="12"/>
     </row>
     <row r="12" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="19"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
       <c r="D12" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="19">
         <v>22</v>
       </c>
       <c r="F12" s="12">
@@ -1344,13 +1344,13 @@
         <f t="shared" si="4"/>
         <v>-1595</v>
       </c>
-      <c r="N12" s="25">
+      <c r="N12" s="23">
         <f t="shared" si="5"/>
         <v>723.5</v>
       </c>
       <c r="O12" s="15"/>
       <c r="P12" s="15"/>
-      <c r="Q12" s="21"/>
+      <c r="Q12" s="20"/>
       <c r="R12" s="12"/>
       <c r="S12" s="12"/>
       <c r="T12" s="12"/>
@@ -1364,13 +1364,13 @@
       <c r="AB12" s="12"/>
     </row>
     <row r="13" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="19"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
+      <c r="A13" s="28"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="28"/>
       <c r="D13" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="19">
         <v>1</v>
       </c>
       <c r="F13" s="12">
@@ -1399,13 +1399,13 @@
         <f t="shared" si="4"/>
         <v>3715</v>
       </c>
-      <c r="N13" s="25">
+      <c r="N13" s="23">
         <f t="shared" si="5"/>
         <v>1101.3333333333333</v>
       </c>
       <c r="O13" s="15"/>
       <c r="P13" s="15"/>
-      <c r="Q13" s="21"/>
+      <c r="Q13" s="20"/>
       <c r="R13" s="12"/>
       <c r="S13" s="12"/>
       <c r="T13" s="12"/>
@@ -1419,14 +1419,14 @@
       <c r="AB13" s="12"/>
     </row>
     <row r="14" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="19"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="28"/>
       <c r="D14" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="20">
-        <v>3</v>
+      <c r="E14" s="19">
+        <v>2</v>
       </c>
       <c r="F14" s="12">
         <v>12</v>
@@ -1454,13 +1454,13 @@
         <f t="shared" si="4"/>
         <v>5780</v>
       </c>
-      <c r="N14" s="25">
+      <c r="N14" s="23">
         <f t="shared" si="5"/>
         <v>1404.8333333333333</v>
       </c>
       <c r="O14" s="15"/>
       <c r="P14" s="15"/>
-      <c r="Q14" s="21"/>
+      <c r="Q14" s="20"/>
       <c r="R14" s="12"/>
       <c r="S14" s="12"/>
       <c r="T14" s="12"/>
@@ -1474,14 +1474,14 @@
       <c r="AB14" s="12"/>
     </row>
     <row r="15" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="19"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
+      <c r="A15" s="28"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="28"/>
       <c r="D15" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E15" s="20">
-        <v>20</v>
+      <c r="E15" s="19">
+        <v>19</v>
       </c>
       <c r="F15" s="12">
         <v>12</v>
@@ -1509,13 +1509,13 @@
         <f t="shared" si="4"/>
         <v>5383</v>
       </c>
-      <c r="N15" s="25">
+      <c r="N15" s="23">
         <f t="shared" si="5"/>
         <v>1264.75</v>
       </c>
       <c r="O15" s="15"/>
       <c r="P15" s="15"/>
-      <c r="Q15" s="21"/>
+      <c r="Q15" s="20"/>
       <c r="R15" s="12"/>
       <c r="S15" s="12"/>
       <c r="T15" s="12"/>
@@ -1529,14 +1529,14 @@
       <c r="AB15" s="12"/>
     </row>
     <row r="16" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="19"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
+      <c r="A16" s="28"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="28"/>
       <c r="D16" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="E16" s="20">
-        <v>5</v>
+      <c r="E16" s="19">
+        <v>4</v>
       </c>
       <c r="F16" s="12">
         <v>12</v>
@@ -1564,13 +1564,13 @@
         <f t="shared" si="4"/>
         <v>570</v>
       </c>
-      <c r="N16" s="25">
+      <c r="N16" s="23">
         <f t="shared" si="5"/>
         <v>802.58333333333337</v>
       </c>
       <c r="O16" s="15"/>
       <c r="P16" s="15"/>
-      <c r="Q16" s="21"/>
+      <c r="Q16" s="20"/>
       <c r="R16" s="12"/>
       <c r="S16" s="12"/>
       <c r="T16" s="12"/>
@@ -1584,13 +1584,13 @@
       <c r="AB16" s="12"/>
     </row>
     <row r="17" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="19"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
+      <c r="A17" s="28"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
       <c r="D17" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E17" s="20">
+      <c r="E17" s="19">
         <v>22</v>
       </c>
       <c r="F17" s="12">
@@ -1619,13 +1619,13 @@
         <f t="shared" si="4"/>
         <v>531</v>
       </c>
-      <c r="N17" s="25">
+      <c r="N17" s="23">
         <f t="shared" si="5"/>
         <v>942.75</v>
       </c>
       <c r="O17" s="15"/>
       <c r="P17" s="15"/>
-      <c r="Q17" s="21"/>
+      <c r="Q17" s="20"/>
       <c r="R17" s="12"/>
       <c r="S17" s="12"/>
       <c r="T17" s="12"/>
@@ -1639,11 +1639,11 @@
       <c r="AB17" s="12"/>
     </row>
     <row r="18" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
       <c r="D18" s="12" t="s">
         <v>32</v>
       </c>
@@ -1683,10 +1683,10 @@
       <c r="P18" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="Q18" s="21" t="s">
+      <c r="Q18" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="R18" s="21"/>
+      <c r="R18" s="20"/>
       <c r="T18" s="12"/>
       <c r="U18" s="12"/>
       <c r="V18" s="12"/>
@@ -1698,24 +1698,24 @@
       <c r="AB18" s="12"/>
     </row>
     <row r="19" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="22" t="s">
+      <c r="A19" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
       <c r="D19" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="E19" s="20">
+      <c r="E19" s="19">
         <v>1</v>
       </c>
-      <c r="F19" s="27">
+      <c r="F19" s="25">
         <v>10.83</v>
       </c>
-      <c r="G19" s="28">
+      <c r="G19" s="26">
         <v>5.58</v>
       </c>
-      <c r="H19" s="29">
+      <c r="H19" s="27">
         <v>5.25</v>
       </c>
       <c r="I19" s="12">
@@ -1728,7 +1728,7 @@
         <f>(H19+I19)/J19</f>
         <v>3.9709090909090907</v>
       </c>
-      <c r="L19" s="26">
+      <c r="L19" s="24">
         <v>3101.25</v>
       </c>
       <c r="M19" s="12">
@@ -1742,15 +1742,15 @@
         <f>O2</f>
         <v>0.75</v>
       </c>
-      <c r="P19" s="24">
+      <c r="P19" s="22">
         <f>O19*P2</f>
         <v>0.66674999999999995</v>
       </c>
-      <c r="Q19" s="23">
+      <c r="Q19" s="21">
         <f>P19*Q2</f>
         <v>0.16668749999999999</v>
       </c>
-      <c r="R19" s="21"/>
+      <c r="R19" s="20"/>
       <c r="T19" s="12"/>
       <c r="U19" s="12"/>
       <c r="V19" s="12"/>
@@ -1762,22 +1762,22 @@
       <c r="AB19" s="12"/>
     </row>
     <row r="20" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="19"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
       <c r="D20" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="E20" s="20">
-        <v>3</v>
-      </c>
-      <c r="F20" s="27">
+      <c r="E20" s="19">
+        <v>2</v>
+      </c>
+      <c r="F20" s="25">
         <v>8.92</v>
       </c>
-      <c r="G20" s="28">
+      <c r="G20" s="26">
         <v>4.33</v>
       </c>
-      <c r="H20" s="29">
+      <c r="H20" s="27">
         <v>4.58</v>
       </c>
       <c r="I20" s="12">
@@ -1790,7 +1790,7 @@
         <f>(H20+I20)/J20</f>
         <v>2.7318611987381702</v>
       </c>
-      <c r="L20" s="26">
+      <c r="L20" s="24">
         <v>3993.08</v>
       </c>
       <c r="M20" s="12">
@@ -1804,15 +1804,15 @@
         <f t="shared" ref="O20:O23" si="7">O3</f>
         <v>0.75</v>
       </c>
-      <c r="P20" s="24">
+      <c r="P20" s="22">
         <f t="shared" ref="P20:Q23" si="8">O20*P3</f>
         <v>0.50025000000000008</v>
       </c>
-      <c r="Q20" s="23">
+      <c r="Q20" s="21">
         <f t="shared" si="8"/>
         <v>8.3541750000000012E-2</v>
       </c>
-      <c r="R20" s="21"/>
+      <c r="R20" s="20"/>
       <c r="T20" s="12"/>
       <c r="U20" s="12"/>
       <c r="V20" s="12"/>
@@ -1824,22 +1824,22 @@
       <c r="AB20" s="12"/>
     </row>
     <row r="21" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
+      <c r="A21" s="28"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="28"/>
       <c r="D21" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="20">
-        <v>20</v>
-      </c>
-      <c r="F21" s="27">
+      <c r="E21" s="19">
+        <v>19</v>
+      </c>
+      <c r="F21" s="25">
         <v>4.75</v>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="26">
         <v>1.25</v>
       </c>
-      <c r="H21" s="29">
+      <c r="H21" s="27">
         <v>3.5</v>
       </c>
       <c r="I21" s="12">
@@ -1849,10 +1849,10 @@
         <v>3.42</v>
       </c>
       <c r="K21" s="13">
-        <f t="shared" ref="K20:K23" si="9">(H21+I21)/J21</f>
+        <f t="shared" ref="K21:K23" si="9">(H21+I21)/J21</f>
         <v>2.0964912280701755</v>
       </c>
-      <c r="L21" s="26">
+      <c r="L21" s="24">
         <v>2574.92</v>
       </c>
       <c r="M21" s="12">
@@ -1866,15 +1866,15 @@
         <f t="shared" si="7"/>
         <v>0.33300000000000002</v>
       </c>
-      <c r="P21" s="24">
+      <c r="P21" s="22">
         <f t="shared" si="8"/>
         <v>8.3250000000000005E-2</v>
       </c>
-      <c r="Q21" s="23">
+      <c r="Q21" s="21">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="R21" s="21"/>
+      <c r="R21" s="20"/>
       <c r="T21" s="12"/>
       <c r="U21" s="12"/>
       <c r="V21" s="12"/>
@@ -1886,22 +1886,22 @@
       <c r="AB21" s="12"/>
     </row>
     <row r="22" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
+      <c r="A22" s="28"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="28"/>
       <c r="D22" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="E22" s="20">
-        <v>5</v>
-      </c>
-      <c r="F22" s="27">
+      <c r="E22" s="19">
+        <v>4</v>
+      </c>
+      <c r="F22" s="25">
         <v>8.25</v>
       </c>
-      <c r="G22" s="28">
+      <c r="G22" s="26">
         <v>4.08</v>
       </c>
-      <c r="H22" s="29">
+      <c r="H22" s="27">
         <v>4.17</v>
       </c>
       <c r="I22" s="12">
@@ -1914,7 +1914,7 @@
         <f t="shared" si="9"/>
         <v>3.0035335689045937</v>
       </c>
-      <c r="L22" s="26">
+      <c r="L22" s="24">
         <v>2689.08</v>
       </c>
       <c r="M22" s="12">
@@ -1928,15 +1928,15 @@
         <f t="shared" si="7"/>
         <v>0.66700000000000004</v>
       </c>
-      <c r="P22" s="24">
+      <c r="P22" s="22">
         <f t="shared" si="8"/>
         <v>0.416875</v>
       </c>
-      <c r="Q22" s="23">
+      <c r="Q22" s="21">
         <f t="shared" si="8"/>
         <v>0.16675000000000001</v>
       </c>
-      <c r="R22" s="21"/>
+      <c r="R22" s="20"/>
       <c r="T22" s="12"/>
       <c r="U22" s="12"/>
       <c r="V22" s="12"/>
@@ -1948,22 +1948,22 @@
       <c r="AB22" s="12"/>
     </row>
     <row r="23" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
+      <c r="A23" s="28"/>
+      <c r="B23" s="28"/>
+      <c r="C23" s="28"/>
       <c r="D23" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E23" s="20">
+      <c r="E23" s="19">
         <v>22</v>
       </c>
-      <c r="F23" s="27">
+      <c r="F23" s="25">
         <v>4.5</v>
       </c>
-      <c r="G23" s="28">
+      <c r="G23" s="26">
         <v>2.75</v>
       </c>
-      <c r="H23" s="29">
+      <c r="H23" s="27">
         <v>1.75</v>
       </c>
       <c r="I23" s="12">
@@ -1976,7 +1976,7 @@
         <f t="shared" si="9"/>
         <v>1.102102102102102</v>
       </c>
-      <c r="L23" s="26">
+      <c r="L23" s="24">
         <v>2161.33</v>
       </c>
       <c r="M23" s="12">
@@ -1990,15 +1990,15 @@
         <f t="shared" si="7"/>
         <v>0.66700000000000004</v>
       </c>
-      <c r="P23" s="24">
+      <c r="P23" s="22">
         <f t="shared" si="8"/>
         <v>0.25012500000000004</v>
       </c>
-      <c r="Q23" s="23">
+      <c r="Q23" s="21">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="R23" s="21"/>
+      <c r="R23" s="20"/>
       <c r="T23" s="12"/>
       <c r="U23" s="12"/>
       <c r="V23" s="12"/>
@@ -2010,11 +2010,11 @@
       <c r="AB23" s="12"/>
     </row>
     <row r="24" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="19"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
+      <c r="A24" s="28"/>
+      <c r="B24" s="28"/>
+      <c r="C24" s="28"/>
       <c r="D24" s="12"/>
-      <c r="E24" s="20"/>
+      <c r="E24" s="19"/>
       <c r="F24" s="12"/>
       <c r="G24" s="12"/>
       <c r="H24" s="12"/>
@@ -2040,11 +2040,11 @@
       <c r="AB24" s="12"/>
     </row>
     <row r="25" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="19"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
+      <c r="A25" s="28"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="28"/>
       <c r="D25" s="12"/>
-      <c r="E25" s="20"/>
+      <c r="E25" s="19"/>
       <c r="F25" s="12"/>
       <c r="G25" s="12"/>
       <c r="H25" s="12"/>
@@ -2070,11 +2070,11 @@
       <c r="AB25" s="12"/>
     </row>
     <row r="26" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="19"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
+      <c r="A26" s="28"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="28"/>
       <c r="D26" s="12"/>
-      <c r="E26" s="20"/>
+      <c r="E26" s="19"/>
       <c r="F26" s="12"/>
       <c r="G26" s="12"/>
       <c r="H26" s="12"/>
@@ -2100,11 +2100,11 @@
       <c r="AB26" s="12"/>
     </row>
     <row r="27" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="19"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
+      <c r="A27" s="28"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="28"/>
       <c r="D27" s="12"/>
-      <c r="E27" s="20"/>
+      <c r="E27" s="19"/>
       <c r="F27" s="12"/>
       <c r="G27" s="12"/>
       <c r="H27" s="12"/>
@@ -2130,11 +2130,11 @@
       <c r="AB27" s="12"/>
     </row>
     <row r="28" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="19"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
+      <c r="A28" s="28"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="28"/>
       <c r="D28" s="12"/>
-      <c r="E28" s="20"/>
+      <c r="E28" s="19"/>
       <c r="F28" s="12"/>
       <c r="G28" s="12"/>
       <c r="H28" s="12"/>
@@ -2430,9 +2430,9 @@
       <c r="AB37" s="11"/>
     </row>
     <row r="38" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="19"/>
-      <c r="B38" s="19"/>
-      <c r="C38" s="19"/>
+      <c r="A38" s="28"/>
+      <c r="B38" s="28"/>
+      <c r="C38" s="28"/>
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
@@ -2460,9 +2460,9 @@
       <c r="AB38" s="11"/>
     </row>
     <row r="39" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="19"/>
-      <c r="B39" s="19"/>
-      <c r="C39" s="19"/>
+      <c r="A39" s="28"/>
+      <c r="B39" s="28"/>
+      <c r="C39" s="28"/>
       <c r="D39" s="11"/>
       <c r="E39" s="17"/>
       <c r="F39" s="17"/>
@@ -2490,9 +2490,9 @@
       <c r="AB39" s="11"/>
     </row>
     <row r="40" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="19"/>
-      <c r="B40" s="19"/>
-      <c r="C40" s="19"/>
+      <c r="A40" s="28"/>
+      <c r="B40" s="28"/>
+      <c r="C40" s="28"/>
       <c r="D40" s="11"/>
       <c r="E40" s="17"/>
       <c r="F40" s="11"/>
@@ -2520,9 +2520,9 @@
       <c r="AB40" s="11"/>
     </row>
     <row r="41" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="19"/>
-      <c r="B41" s="19"/>
-      <c r="C41" s="19"/>
+      <c r="A41" s="28"/>
+      <c r="B41" s="28"/>
+      <c r="C41" s="28"/>
       <c r="D41" s="11"/>
       <c r="E41" s="17"/>
       <c r="F41" s="11"/>
@@ -2550,9 +2550,9 @@
       <c r="AB41" s="11"/>
     </row>
     <row r="42" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="19"/>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
+      <c r="A42" s="28"/>
+      <c r="B42" s="28"/>
+      <c r="C42" s="28"/>
       <c r="D42" s="11"/>
       <c r="E42" s="17"/>
       <c r="F42" s="11"/>
@@ -2580,9 +2580,9 @@
       <c r="AB42" s="11"/>
     </row>
     <row r="43" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="19"/>
-      <c r="B43" s="19"/>
-      <c r="C43" s="19"/>
+      <c r="A43" s="28"/>
+      <c r="B43" s="28"/>
+      <c r="C43" s="28"/>
       <c r="D43" s="11"/>
       <c r="E43" s="17"/>
       <c r="F43" s="11"/>
@@ -2610,9 +2610,9 @@
       <c r="AB43" s="11"/>
     </row>
     <row r="44" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="19"/>
-      <c r="B44" s="19"/>
-      <c r="C44" s="19"/>
+      <c r="A44" s="28"/>
+      <c r="B44" s="28"/>
+      <c r="C44" s="28"/>
       <c r="D44" s="11"/>
       <c r="E44" s="17"/>
       <c r="F44" s="11"/>
@@ -2640,9 +2640,9 @@
       <c r="AB44" s="11"/>
     </row>
     <row r="45" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="19"/>
-      <c r="B45" s="19"/>
-      <c r="C45" s="19"/>
+      <c r="A45" s="28"/>
+      <c r="B45" s="28"/>
+      <c r="C45" s="28"/>
       <c r="D45" s="11"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
@@ -2670,9 +2670,9 @@
       <c r="AB45" s="11"/>
     </row>
     <row r="46" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="19"/>
-      <c r="B46" s="19"/>
-      <c r="C46" s="19"/>
+      <c r="A46" s="28"/>
+      <c r="B46" s="28"/>
+      <c r="C46" s="28"/>
       <c r="D46" s="11"/>
       <c r="E46" s="17"/>
       <c r="F46" s="11"/>
@@ -2700,9 +2700,9 @@
       <c r="AB46" s="11"/>
     </row>
     <row r="47" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="19"/>
-      <c r="B47" s="19"/>
-      <c r="C47" s="19"/>
+      <c r="A47" s="28"/>
+      <c r="B47" s="28"/>
+      <c r="C47" s="28"/>
       <c r="D47" s="11"/>
       <c r="E47" s="17"/>
       <c r="F47" s="11"/>
@@ -2730,9 +2730,9 @@
       <c r="AB47" s="11"/>
     </row>
     <row r="48" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="19"/>
-      <c r="B48" s="19"/>
-      <c r="C48" s="19"/>
+      <c r="A48" s="28"/>
+      <c r="B48" s="28"/>
+      <c r="C48" s="28"/>
       <c r="D48" s="11"/>
       <c r="E48" s="17"/>
       <c r="F48" s="11"/>
@@ -2760,9 +2760,9 @@
       <c r="AB48" s="11"/>
     </row>
     <row r="49" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="19"/>
-      <c r="B49" s="19"/>
-      <c r="C49" s="19"/>
+      <c r="A49" s="28"/>
+      <c r="B49" s="28"/>
+      <c r="C49" s="28"/>
       <c r="D49" s="11"/>
       <c r="E49" s="17"/>
       <c r="F49" s="11"/>
@@ -2790,9 +2790,9 @@
       <c r="AB49" s="11"/>
     </row>
     <row r="50" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="19"/>
-      <c r="B50" s="19"/>
-      <c r="C50" s="19"/>
+      <c r="A50" s="28"/>
+      <c r="B50" s="28"/>
+      <c r="C50" s="28"/>
       <c r="D50" s="11"/>
       <c r="E50" s="17"/>
       <c r="F50" s="11"/>
@@ -2820,9 +2820,9 @@
       <c r="AB50" s="11"/>
     </row>
     <row r="51" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="19"/>
-      <c r="B51" s="19"/>
-      <c r="C51" s="19"/>
+      <c r="A51" s="28"/>
+      <c r="B51" s="28"/>
+      <c r="C51" s="28"/>
       <c r="D51" s="11"/>
       <c r="E51" s="17"/>
       <c r="F51" s="11"/>
@@ -2850,9 +2850,9 @@
       <c r="AB51" s="11"/>
     </row>
     <row r="52" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="19"/>
-      <c r="B52" s="19"/>
-      <c r="C52" s="19"/>
+      <c r="A52" s="28"/>
+      <c r="B52" s="28"/>
+      <c r="C52" s="28"/>
       <c r="D52" s="11"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
@@ -2880,9 +2880,9 @@
       <c r="AB52" s="11"/>
     </row>
     <row r="53" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="19"/>
-      <c r="B53" s="19"/>
-      <c r="C53" s="19"/>
+      <c r="A53" s="28"/>
+      <c r="B53" s="28"/>
+      <c r="C53" s="28"/>
       <c r="D53" s="11"/>
       <c r="E53" s="17"/>
       <c r="F53" s="11"/>
@@ -2910,9 +2910,9 @@
       <c r="AB53" s="11"/>
     </row>
     <row r="54" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="19"/>
-      <c r="B54" s="19"/>
-      <c r="C54" s="19"/>
+      <c r="A54" s="28"/>
+      <c r="B54" s="28"/>
+      <c r="C54" s="28"/>
       <c r="D54" s="11"/>
       <c r="E54" s="17"/>
       <c r="F54" s="11"/>
@@ -2940,9 +2940,9 @@
       <c r="AB54" s="11"/>
     </row>
     <row r="55" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="19"/>
-      <c r="B55" s="19"/>
-      <c r="C55" s="19"/>
+      <c r="A55" s="28"/>
+      <c r="B55" s="28"/>
+      <c r="C55" s="28"/>
       <c r="D55" s="11"/>
       <c r="E55" s="17"/>
       <c r="F55" s="11"/>
@@ -2970,9 +2970,9 @@
       <c r="AB55" s="11"/>
     </row>
     <row r="56" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="19"/>
-      <c r="B56" s="19"/>
-      <c r="C56" s="19"/>
+      <c r="A56" s="28"/>
+      <c r="B56" s="28"/>
+      <c r="C56" s="28"/>
       <c r="D56" s="11"/>
       <c r="E56" s="17"/>
       <c r="F56" s="11"/>
@@ -3000,9 +3000,9 @@
       <c r="AB56" s="11"/>
     </row>
     <row r="57" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="19"/>
-      <c r="B57" s="19"/>
-      <c r="C57" s="19"/>
+      <c r="A57" s="28"/>
+      <c r="B57" s="28"/>
+      <c r="C57" s="28"/>
       <c r="D57" s="11"/>
       <c r="E57" s="17"/>
       <c r="F57" s="11"/>
@@ -3030,9 +3030,9 @@
       <c r="AB57" s="11"/>
     </row>
     <row r="58" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="19"/>
-      <c r="B58" s="19"/>
-      <c r="C58" s="19"/>
+      <c r="A58" s="28"/>
+      <c r="B58" s="28"/>
+      <c r="C58" s="28"/>
       <c r="D58" s="11"/>
       <c r="E58" s="17"/>
       <c r="F58" s="11"/>
@@ -3060,9 +3060,9 @@
       <c r="AB58" s="11"/>
     </row>
     <row r="59" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="19"/>
-      <c r="B59" s="19"/>
-      <c r="C59" s="19"/>
+      <c r="A59" s="28"/>
+      <c r="B59" s="28"/>
+      <c r="C59" s="28"/>
       <c r="D59" s="11"/>
       <c r="E59" s="11"/>
       <c r="F59" s="11"/>
@@ -3090,9 +3090,9 @@
       <c r="AB59" s="11"/>
     </row>
     <row r="60" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="19"/>
-      <c r="B60" s="19"/>
-      <c r="C60" s="19"/>
+      <c r="A60" s="28"/>
+      <c r="B60" s="28"/>
+      <c r="C60" s="28"/>
       <c r="D60" s="11"/>
       <c r="E60" s="17"/>
       <c r="F60" s="11"/>
@@ -3120,9 +3120,9 @@
       <c r="AB60" s="11"/>
     </row>
     <row r="61" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="19"/>
-      <c r="B61" s="19"/>
-      <c r="C61" s="19"/>
+      <c r="A61" s="28"/>
+      <c r="B61" s="28"/>
+      <c r="C61" s="28"/>
       <c r="D61" s="11"/>
       <c r="E61" s="17"/>
       <c r="F61" s="11"/>
@@ -3150,9 +3150,9 @@
       <c r="AB61" s="11"/>
     </row>
     <row r="62" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="19"/>
-      <c r="B62" s="19"/>
-      <c r="C62" s="19"/>
+      <c r="A62" s="28"/>
+      <c r="B62" s="28"/>
+      <c r="C62" s="28"/>
       <c r="D62" s="11"/>
       <c r="E62" s="17"/>
       <c r="F62" s="11"/>
@@ -3180,9 +3180,9 @@
       <c r="AB62" s="11"/>
     </row>
     <row r="63" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="19"/>
-      <c r="B63" s="19"/>
-      <c r="C63" s="19"/>
+      <c r="A63" s="28"/>
+      <c r="B63" s="28"/>
+      <c r="C63" s="28"/>
       <c r="D63" s="11"/>
       <c r="E63" s="17"/>
       <c r="F63" s="11"/>
@@ -3210,9 +3210,9 @@
       <c r="AB63" s="11"/>
     </row>
     <row r="64" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="19"/>
-      <c r="B64" s="19"/>
-      <c r="C64" s="19"/>
+      <c r="A64" s="28"/>
+      <c r="B64" s="28"/>
+      <c r="C64" s="28"/>
       <c r="D64" s="11"/>
       <c r="E64" s="17"/>
       <c r="F64" s="11"/>
@@ -3240,9 +3240,9 @@
       <c r="AB64" s="11"/>
     </row>
     <row r="65" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="19"/>
-      <c r="B65" s="19"/>
-      <c r="C65" s="19"/>
+      <c r="A65" s="28"/>
+      <c r="B65" s="28"/>
+      <c r="C65" s="28"/>
       <c r="D65" s="11"/>
       <c r="E65" s="17"/>
       <c r="F65" s="11"/>
@@ -3571,6 +3571,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A60:C65"/>
+    <mergeCell ref="A39:C44"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A46:C51"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A53:C58"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="A2:C6"/>
@@ -3579,13 +3586,6 @@
     <mergeCell ref="A8:C17"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A60:C65"/>
-    <mergeCell ref="A39:C44"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A46:C51"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A53:C58"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/数据对比/cn队数据整理/year6-s1-R1.xlsx
+++ b/数据对比/cn队数据整理/year6-s1-R1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\best igl wiki\数据对比\cn队数据整理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5243BC30-4F0B-4AD4-B869-CC00C3A40DFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C3E759F-FE08-4012-A315-BA86E712A27F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-31087" yWindow="-109" windowWidth="31196" windowHeight="18974" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -99,10 +99,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Beiyun (EDG)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>IGL status</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -220,6 +216,10 @@
   </si>
   <si>
     <t>Kills Pts</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bieyun (EDG)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -667,7 +667,7 @@
   <sheetData>
     <row r="1" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -727,7 +727,7 @@
     </row>
     <row r="2" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -976,7 +976,7 @@
       <c r="B6" s="28"/>
       <c r="C6" s="28"/>
       <c r="D6" s="11" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="E6" s="19">
         <v>22</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="7" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B7" s="28"/>
       <c r="C7" s="28"/>
@@ -1088,12 +1088,12 @@
     </row>
     <row r="8" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" s="28"/>
       <c r="C8" s="28"/>
       <c r="D8" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E8" s="19">
         <v>1</v>
@@ -1148,7 +1148,7 @@
       <c r="B9" s="28"/>
       <c r="C9" s="28"/>
       <c r="D9" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E9" s="19">
         <v>2</v>
@@ -1203,7 +1203,7 @@
       <c r="B10" s="28"/>
       <c r="C10" s="28"/>
       <c r="D10" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E10" s="19">
         <v>19</v>
@@ -1258,7 +1258,7 @@
       <c r="B11" s="28"/>
       <c r="C11" s="28"/>
       <c r="D11" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E11" s="19">
         <v>4</v>
@@ -1313,7 +1313,7 @@
       <c r="B12" s="28"/>
       <c r="C12" s="28"/>
       <c r="D12" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E12" s="19">
         <v>22</v>
@@ -1368,7 +1368,7 @@
       <c r="B13" s="28"/>
       <c r="C13" s="28"/>
       <c r="D13" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E13" s="19">
         <v>1</v>
@@ -1423,7 +1423,7 @@
       <c r="B14" s="28"/>
       <c r="C14" s="28"/>
       <c r="D14" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E14" s="19">
         <v>2</v>
@@ -1478,7 +1478,7 @@
       <c r="B15" s="28"/>
       <c r="C15" s="28"/>
       <c r="D15" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E15" s="19">
         <v>19</v>
@@ -1533,7 +1533,7 @@
       <c r="B16" s="28"/>
       <c r="C16" s="28"/>
       <c r="D16" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E16" s="19">
         <v>4</v>
@@ -1588,7 +1588,7 @@
       <c r="B17" s="28"/>
       <c r="C17" s="28"/>
       <c r="D17" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E17" s="19">
         <v>22</v>
@@ -1640,51 +1640,51 @@
     </row>
     <row r="18" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B18" s="28"/>
       <c r="C18" s="28"/>
       <c r="D18" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E18" s="12" t="s">
         <v>1</v>
       </c>
       <c r="F18" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="G18" s="12" t="s">
+      <c r="H18" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="H18" s="12" t="s">
-        <v>50</v>
-      </c>
       <c r="I18" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="J18" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="J18" s="12" t="s">
+      <c r="K18" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="K18" s="12" t="s">
+      <c r="L18" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="L18" s="12" t="s">
+      <c r="M18" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="M18" s="12" t="s">
+      <c r="N18" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="N18" s="12" t="s">
+      <c r="O18" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="O18" s="12" t="s">
+      <c r="P18" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="P18" s="12" t="s">
+      <c r="Q18" s="20" t="s">
         <v>45</v>
-      </c>
-      <c r="Q18" s="20" t="s">
-        <v>46</v>
       </c>
       <c r="R18" s="20"/>
       <c r="T18" s="12"/>
@@ -1699,12 +1699,12 @@
     </row>
     <row r="19" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B19" s="28"/>
       <c r="C19" s="28"/>
       <c r="D19" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E19" s="19">
         <v>1</v>
@@ -1766,7 +1766,7 @@
       <c r="B20" s="28"/>
       <c r="C20" s="28"/>
       <c r="D20" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E20" s="19">
         <v>2</v>
@@ -1828,7 +1828,7 @@
       <c r="B21" s="28"/>
       <c r="C21" s="28"/>
       <c r="D21" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E21" s="19">
         <v>19</v>
@@ -1890,7 +1890,7 @@
       <c r="B22" s="28"/>
       <c r="C22" s="28"/>
       <c r="D22" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E22" s="19">
         <v>4</v>
@@ -1952,7 +1952,7 @@
       <c r="B23" s="28"/>
       <c r="C23" s="28"/>
       <c r="D23" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E23" s="19">
         <v>22</v>
@@ -3571,13 +3571,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A60:C65"/>
-    <mergeCell ref="A39:C44"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A46:C51"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A53:C58"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="A2:C6"/>
@@ -3586,6 +3579,13 @@
     <mergeCell ref="A8:C17"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A60:C65"/>
+    <mergeCell ref="A39:C44"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A46:C51"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A53:C58"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
